--- a/ARM Functions/Ability Edits/Zen Mode.xlsx
+++ b/ARM Functions/Ability Edits/Zen Mode.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\ROM\3ds\USUM ARM research\Ability Edits\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5458464-B853-42A6-8D8F-56973E73FFC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EB9E4F1-75B3-4D69-95C2-9A1FDB5E8E3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18120" xr2:uid="{664BA6B8-043A-4EF3-A83B-BDEF02BD0490}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16457" windowHeight="17914" xr2:uid="{664BA6B8-043A-4EF3-A83B-BDEF02BD0490}"/>
   </bookViews>
   <sheets>
     <sheet name="edit" sheetId="4" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="241">
   <si>
     <t>Main</t>
   </si>
@@ -381,18 +381,9 @@
     <t>target odd forme</t>
   </si>
   <si>
-    <t>is r1 odd?</t>
-  </si>
-  <si>
     <t>go to target even forme</t>
   </si>
   <si>
-    <t>forme is odd, subtract 1 to awake</t>
-  </si>
-  <si>
-    <t xml:space="preserve">forme is even, add 1 to become zen </t>
-  </si>
-  <si>
     <t>check if forme changed</t>
   </si>
   <si>
@@ -402,12 +393,6 @@
     <t>tst r5, 0x1</t>
   </si>
   <si>
-    <t>addne r5, r5, 0x1</t>
-  </si>
-  <si>
-    <t>subeq r5, r5, 0x1</t>
-  </si>
-  <si>
     <t>is new forme odd?</t>
   </si>
   <si>
@@ -444,9 +429,6 @@
     <t>forme 2, 3 are Galarian</t>
   </si>
   <si>
-    <t>bl 0x000003B0</t>
-  </si>
-  <si>
     <t>check if move is special or Physical</t>
   </si>
   <si>
@@ -513,84 +495,39 @@
     <t>Zen Mode Forme Change from attack 0x27</t>
   </si>
   <si>
-    <t>00101428</t>
-  </si>
-  <si>
     <t>r0 = [0 = go to even, 1 = go to odd] r6 = self index, r7 = self pointer, r8 = base pointer</t>
   </si>
   <si>
     <t>010050E3</t>
   </si>
   <si>
-    <t>0200001A</t>
-  </si>
-  <si>
     <t>010015E3</t>
   </si>
   <si>
-    <t>01508512</t>
-  </si>
-  <si>
-    <t>010000EA</t>
-  </si>
-  <si>
-    <t>01504502</t>
-  </si>
-  <si>
-    <t>9543FEEB</t>
-  </si>
-  <si>
-    <t>1F00001A</t>
-  </si>
-  <si>
     <t>1200A0E3</t>
   </si>
   <si>
-    <t>BE19FEEB</t>
-  </si>
-  <si>
     <t>3912D7E5</t>
   </si>
   <si>
     <t>010051E3</t>
   </si>
   <si>
-    <t>0800008A</t>
-  </si>
-  <si>
     <t>0300A0E3</t>
   </si>
   <si>
-    <t>B919FEEB</t>
-  </si>
-  <si>
     <t>060050E1</t>
   </si>
   <si>
-    <t>1600001A</t>
-  </si>
-  <si>
-    <t>CCFBFBEB</t>
-  </si>
-  <si>
-    <t>51FBFBEB</t>
-  </si>
-  <si>
     <t>0030A0E1</t>
   </si>
   <si>
-    <t>AE19FEEB</t>
-  </si>
-  <si>
     <t>0300000A</t>
   </si>
   <si>
     <t>0400A0E3</t>
   </si>
   <si>
-    <t>AA19FEEB</t>
-  </si>
-  <si>
     <t>0700001A</t>
   </si>
   <si>
@@ -630,9 +567,6 @@
     <t>0000A083</t>
   </si>
   <si>
-    <t>38A000EA</t>
-  </si>
-  <si>
     <t>special 2 -&gt;1, Physical 1 -&gt; 0</t>
   </si>
   <si>
@@ -657,26 +591,182 @@
     <t>0100A093</t>
   </si>
   <si>
-    <t>ldrb r5, [r7, 0x239]</t>
-  </si>
-  <si>
-    <t>3952D7E5</t>
-  </si>
-  <si>
-    <t>7918FEEB</t>
-  </si>
-  <si>
-    <t>CA21FEEB</t>
-  </si>
-  <si>
-    <t>E8EDFDEA</t>
+    <t>ldrb r3, [r7, 0x239]</t>
+  </si>
+  <si>
+    <t>tst r3, 0x1</t>
+  </si>
+  <si>
+    <t>cmp r3, r5</t>
+  </si>
+  <si>
+    <t>3932D7E5</t>
+  </si>
+  <si>
+    <t>010013E3</t>
+  </si>
+  <si>
+    <t>050053E1</t>
+  </si>
+  <si>
+    <t>store new forme</t>
+  </si>
+  <si>
+    <t>store self index</t>
+  </si>
+  <si>
+    <t>check forme mod 2</t>
+  </si>
+  <si>
+    <t>subne r5, r3, 0x1</t>
+  </si>
+  <si>
+    <t>current forme is odd, subtract 1</t>
+  </si>
+  <si>
+    <t>addeq r5, r3, 0x1</t>
+  </si>
+  <si>
+    <t>current forme is even, add 1</t>
+  </si>
+  <si>
+    <t>moveq r2, 0xCD</t>
+  </si>
+  <si>
+    <t>movne r2, 0xCC</t>
+  </si>
+  <si>
+    <t>01508302</t>
+  </si>
+  <si>
+    <t>01504312</t>
+  </si>
+  <si>
+    <t>CC20A013</t>
+  </si>
+  <si>
+    <t>CD20A003</t>
+  </si>
+  <si>
+    <t>push {r4, r5, r6, r7, r8, r10, lr}</t>
+  </si>
+  <si>
+    <t>mov r10, r0</t>
+  </si>
+  <si>
+    <t>mov r0, r10</t>
+  </si>
+  <si>
+    <t>001011EC</t>
+  </si>
+  <si>
+    <t>F0452DE9</t>
+  </si>
+  <si>
+    <t>2444FEEB</t>
+  </si>
+  <si>
+    <t>2100001A</t>
+  </si>
+  <si>
+    <t>4D1AFEEB</t>
+  </si>
+  <si>
+    <t>00A0A0E1</t>
+  </si>
+  <si>
+    <t>0900008A</t>
+  </si>
+  <si>
+    <t>471AFEEB</t>
+  </si>
+  <si>
+    <t>1700001A</t>
+  </si>
+  <si>
+    <t>0A00A0E1</t>
+  </si>
+  <si>
+    <t>DEFBFBEB</t>
+  </si>
+  <si>
+    <t>3B1AFEEB</t>
+  </si>
+  <si>
+    <t>371AFEEB</t>
+  </si>
+  <si>
+    <t>F085BDE8</t>
+  </si>
+  <si>
+    <t>F045BDE8</t>
+  </si>
+  <si>
+    <t>AB9F00EA</t>
+  </si>
+  <si>
+    <t>0300001A</t>
+  </si>
+  <si>
+    <t>1900001A</t>
+  </si>
+  <si>
+    <t>020000EA</t>
+  </si>
+  <si>
+    <t>1500000A</t>
+  </si>
+  <si>
+    <t>0419FEEB</t>
+  </si>
+  <si>
+    <t>5522FEEB</t>
+  </si>
+  <si>
+    <t>73EEFDEA</t>
+  </si>
+  <si>
+    <t>bl 0x000003A8</t>
+  </si>
+  <si>
+    <t>57FCFBEB</t>
+  </si>
+  <si>
+    <t>Zen Mode Forme Change End 0x81/0xA6</t>
+  </si>
+  <si>
+    <t>000DD018</t>
+  </si>
+  <si>
+    <t>mov r0, 0x2</t>
+  </si>
+  <si>
+    <t>0200A0E3</t>
+  </si>
+  <si>
+    <t>CAAAFEEB</t>
+  </si>
+  <si>
+    <t>0900001A</t>
+  </si>
+  <si>
+    <t>95D4FEEB</t>
+  </si>
+  <si>
+    <t>0100A0E3</t>
+  </si>
+  <si>
+    <t>919000EA</t>
+  </si>
+  <si>
+    <t>go to even (Standard)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -795,7 +885,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -874,6 +964,9 @@
     <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="11" fontId="2" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1208,19 +1301,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDB723FF-BCC0-4C2B-BBFA-83B683128D8B}">
-  <dimension ref="A1:F112"/>
-  <sheetFormatPr defaultRowHeight="15.9" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:F136"/>
+  <sheetFormatPr defaultColWidth="9.2109375" defaultRowHeight="15.9"/>
   <cols>
-    <col min="1" max="1" width="10.84375" style="2" customWidth="1"/>
-    <col min="2" max="2" width="10.07421875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.765625" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.85546875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="10.0703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.640625" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="44" style="21" customWidth="1"/>
-    <col min="5" max="8" width="9.23046875" style="2"/>
-    <col min="9" max="11" width="2.3046875" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.23046875" style="2"/>
+    <col min="5" max="8" width="9.2109375" style="2"/>
+    <col min="9" max="11" width="2.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="9.2109375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -1234,7 +1327,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
         <v>92</v>
       </c>
@@ -1242,7 +1335,7 @@
       <c r="C2" s="1"/>
       <c r="D2" s="20"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:6">
       <c r="A3" s="2" t="s">
         <v>99</v>
       </c>
@@ -1251,11 +1344,11 @@
         <v>0410A0E3</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="D3" s="20"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:6">
       <c r="A4" s="2" t="str">
         <f t="shared" ref="A4:A7" si="0">DEC2HEX(HEX2DEC(A3)+4,8)</f>
         <v>000D9EE8</v>
@@ -1268,7 +1361,7 @@
       </c>
       <c r="D4" s="20"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:6">
       <c r="A5" s="2" t="str">
         <f t="shared" si="0"/>
         <v>000D9EEC</v>
@@ -1281,7 +1374,7 @@
       </c>
       <c r="D5" s="20"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:6">
       <c r="A6" s="2" t="str">
         <f t="shared" si="0"/>
         <v>000D9EF0</v>
@@ -1294,7 +1387,7 @@
       </c>
       <c r="D6" s="20"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:6">
       <c r="A7" s="2" t="str">
         <f t="shared" si="0"/>
         <v>000D9EF4</v>
@@ -1307,16 +1400,16 @@
       </c>
       <c r="D7" s="20"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:6">
       <c r="D8" s="20"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:6">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="20"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:6">
       <c r="A10" s="1" t="s">
         <v>105</v>
       </c>
@@ -1324,18 +1417,18 @@
       <c r="C10" s="1"/>
       <c r="D10" s="20"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:6">
       <c r="A11" s="3" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>26</v>
+        <v>207</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
       <c r="A12" s="2" t="str">
         <f t="shared" ref="A12:A33" si="1">DEC2HEX(HEX2DEC(A11)+4,8)</f>
         <v>000D93A0</v>
@@ -1347,7 +1440,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:6">
       <c r="A13" s="2" t="str">
         <f t="shared" si="1"/>
         <v>000D93A4</v>
@@ -1359,7 +1452,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:6">
       <c r="A14" s="4" t="str">
         <f t="shared" si="1"/>
         <v>000D93A8</v>
@@ -1374,7 +1467,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:6">
       <c r="A15" s="4" t="str">
         <f t="shared" si="1"/>
         <v>000D93AC</v>
@@ -1387,13 +1480,13 @@
       </c>
       <c r="D15" s="22"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:6">
       <c r="A16" s="4" t="str">
         <f t="shared" si="1"/>
         <v>000D93B0</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>192</v>
+        <v>171</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>61</v>
@@ -1402,7 +1495,7 @@
       <c r="E16" s="6"/>
       <c r="F16" s="6"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:6">
       <c r="A17" s="4" t="str">
         <f t="shared" si="1"/>
         <v>000D93B4</v>
@@ -1417,7 +1510,7 @@
       <c r="E17" s="6"/>
       <c r="F17" s="6"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:6">
       <c r="A18" s="7" t="str">
         <f t="shared" si="1"/>
         <v>000D93B8</v>
@@ -1434,7 +1527,7 @@
       <c r="E18" s="6"/>
       <c r="F18" s="6"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:6">
       <c r="A19" s="7" t="str">
         <f t="shared" si="1"/>
         <v>000D93BC</v>
@@ -1449,7 +1542,7 @@
       <c r="E19" s="6"/>
       <c r="F19" s="6"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:6">
       <c r="A20" s="7" t="str">
         <f t="shared" si="1"/>
         <v>000D93C0</v>
@@ -1463,13 +1556,13 @@
       <c r="D20" s="23"/>
       <c r="F20" s="6"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:6">
       <c r="A21" s="7" t="str">
         <f t="shared" si="1"/>
         <v>000D93C4</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>193</v>
+        <v>172</v>
       </c>
       <c r="C21" s="7" t="str">
         <f>_xlfn.CONCAT("bne 0x",A$33)</f>
@@ -1479,7 +1572,7 @@
       <c r="E21" s="6"/>
       <c r="F21" s="6"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:6">
       <c r="A22" s="9" t="str">
         <f t="shared" si="1"/>
         <v>000D93C8</v>
@@ -1494,7 +1587,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:6">
       <c r="A23" s="9" t="str">
         <f t="shared" si="1"/>
         <v>000D93CC</v>
@@ -1507,20 +1600,20 @@
       </c>
       <c r="D23" s="24"/>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:6">
       <c r="A24" s="9" t="str">
         <f t="shared" si="1"/>
         <v>000D93D0</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>194</v>
+        <v>173</v>
       </c>
       <c r="C24" s="9" t="s">
         <v>66</v>
       </c>
       <c r="D24" s="24"/>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:6">
       <c r="A25" s="9" t="str">
         <f t="shared" si="1"/>
         <v>000D93D4</v>
@@ -1533,7 +1626,7 @@
       </c>
       <c r="D25" s="24"/>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:6">
       <c r="A26" s="11" t="str">
         <f t="shared" si="1"/>
         <v>000D93D8</v>
@@ -1548,7 +1641,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:6">
       <c r="A27" s="11" t="str">
         <f t="shared" si="1"/>
         <v>000D93DC</v>
@@ -1561,20 +1654,20 @@
       </c>
       <c r="D27" s="26"/>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:6">
       <c r="A28" s="11" t="str">
         <f t="shared" si="1"/>
         <v>000D93E0</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>195</v>
+        <v>174</v>
       </c>
       <c r="C28" s="11" t="s">
         <v>85</v>
       </c>
       <c r="D28" s="25"/>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:6">
       <c r="A29" s="14" t="str">
         <f t="shared" si="1"/>
         <v>000D93E4</v>
@@ -1589,28 +1682,28 @@
         <v>102</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:6">
       <c r="A30" s="2" t="str">
         <f t="shared" si="1"/>
         <v>000D93E8</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>204</v>
+        <v>182</v>
       </c>
       <c r="D30" s="21" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:6">
       <c r="A31" s="2" t="str">
         <f t="shared" si="1"/>
         <v>000D93EC</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>196</v>
+        <v>175</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>108</v>
@@ -1619,55 +1712,56 @@
         <v>110</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:6">
       <c r="A32" s="2" t="str">
         <f t="shared" si="1"/>
         <v>000D93F0</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>197</v>
+        <v>221</v>
       </c>
       <c r="C32" s="2" t="str">
-        <f>_xlfn.CONCAT("b 0x",A$82)</f>
-        <v>b 0x001014D8</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.45">
+        <f>_xlfn.CONCAT("b 0x",A$104)</f>
+        <v>b 0x001012A4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
       <c r="A33" s="2" t="str">
         <f t="shared" si="1"/>
         <v>000D93F4</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>60</v>
+        <v>219</v>
       </c>
       <c r="C33" s="2" t="str">
-        <f>SUBSTITUTE(C110,"lr","pc")</f>
-        <v>pop {r4, r5, r6, r7, r8, pc}</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
+        <f>SUBSTITUTE(C134,"lr","pc")</f>
+        <v>pop {r4, r5, r6, r7, r8, r10, pc}</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
       <c r="A35" s="1" t="s">
-        <v>157</v>
+        <v>231</v>
       </c>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
       <c r="D35" s="20"/>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:4">
       <c r="A36" s="3" t="s">
-        <v>158</v>
+        <v>232</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
+        <v>207</v>
+      </c>
+      <c r="C36" s="2" t="str">
+        <f>C11</f>
+        <v>push {r4, r5, r6, r7, r8, r10, lr}</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
       <c r="A37" s="2" t="str">
-        <f t="shared" ref="A37:A79" si="2">DEC2HEX(HEX2DEC(A36)+4,8)</f>
-        <v>0010142C</v>
+        <f t="shared" ref="A37:A53" si="2">DEC2HEX(HEX2DEC(A36)+4,8)</f>
+        <v>000DD01C</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>27</v>
@@ -1676,10 +1770,10 @@
         <v>16</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:4">
       <c r="A38" s="2" t="str">
         <f t="shared" si="2"/>
-        <v>00101430</v>
+        <v>000DD020</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>28</v>
@@ -1688,1005 +1782,1311 @@
         <v>17</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A39" s="4" t="str">
+    <row r="39" spans="1:4">
+      <c r="A39" s="29" t="str">
         <f t="shared" si="2"/>
-        <v>00101434</v>
-      </c>
-      <c r="B39" s="5" t="s">
+        <v>000DD024</v>
+      </c>
+      <c r="B39" s="29" t="s">
+        <v>234</v>
+      </c>
+      <c r="C39" s="29" t="s">
+        <v>233</v>
+      </c>
+      <c r="D39" s="46"/>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" s="29" t="str">
+        <f t="shared" si="2"/>
+        <v>000DD028</v>
+      </c>
+      <c r="B40" s="29" t="s">
+        <v>235</v>
+      </c>
+      <c r="C40" s="29" t="s">
+        <v>122</v>
+      </c>
+      <c r="D40" s="46"/>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" s="29" t="str">
+        <f t="shared" si="2"/>
+        <v>000DD02C</v>
+      </c>
+      <c r="B41" s="44" t="s">
+        <v>159</v>
+      </c>
+      <c r="C41" s="29" t="s">
+        <v>123</v>
+      </c>
+      <c r="D41" s="46"/>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" s="29" t="str">
+        <f t="shared" si="2"/>
+        <v>000DD030</v>
+      </c>
+      <c r="B42" s="29" t="s">
+        <v>236</v>
+      </c>
+      <c r="C42" s="29" t="str">
+        <f>_xlfn.CONCAT("bne 0x",A53)</f>
+        <v>bne 0x000DD05C</v>
+      </c>
+      <c r="D42" s="46"/>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v>000DD034</v>
+      </c>
+      <c r="B43" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C39" s="4" t="s">
+      <c r="C43" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D39" s="22" t="s">
+      <c r="D43" s="22" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A40" s="4" t="str">
+    <row r="44" spans="1:4">
+      <c r="A44" s="4" t="str">
         <f t="shared" si="2"/>
-        <v>00101438</v>
-      </c>
-      <c r="B40" s="4" t="s">
+        <v>000DD038</v>
+      </c>
+      <c r="B44" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C40" s="4" t="s">
+      <c r="C44" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D40" s="22"/>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A41" s="4" t="str">
+      <c r="D44" s="22"/>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" s="4" t="str">
         <f t="shared" si="2"/>
-        <v>0010143C</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="C41" s="4" t="s">
+        <v>000DD03C</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="C45" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="D41" s="22"/>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A42" s="4" t="str">
+      <c r="D45" s="22"/>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46" s="4" t="str">
         <f t="shared" si="2"/>
-        <v>00101440</v>
-      </c>
-      <c r="B42" s="4" t="s">
+        <v>000DD040</v>
+      </c>
+      <c r="B46" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C42" s="4" t="s">
+      <c r="C46" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D42" s="22"/>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A43" s="7" t="str">
+      <c r="D46" s="22"/>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" s="7" t="str">
         <f t="shared" si="2"/>
-        <v>00101444</v>
-      </c>
-      <c r="B43" s="7" t="s">
+        <v>000DD044</v>
+      </c>
+      <c r="B47" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C43" s="7" t="s">
+      <c r="C47" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="D43" s="23" t="s">
+      <c r="D47" s="23" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A44" s="7" t="str">
+    <row r="48" spans="1:4">
+      <c r="A48" s="7" t="str">
         <f t="shared" si="2"/>
-        <v>00101448</v>
-      </c>
-      <c r="B44" s="7" t="s">
+        <v>000DD048</v>
+      </c>
+      <c r="B48" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="C44" s="7" t="s">
+      <c r="C48" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="D44" s="23"/>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A45" s="7" t="str">
+      <c r="D48" s="23"/>
+    </row>
+    <row r="49" spans="1:4">
+      <c r="A49" s="7" t="str">
         <f t="shared" si="2"/>
-        <v>0010144C</v>
-      </c>
-      <c r="B45" s="7" t="s">
+        <v>000DD04C</v>
+      </c>
+      <c r="B49" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="C45" s="7" t="s">
+      <c r="C49" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="D45" s="23"/>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A46" s="7" t="str">
+      <c r="D49" s="23"/>
+    </row>
+    <row r="50" spans="1:4">
+      <c r="A50" s="7" t="str">
         <f t="shared" si="2"/>
-        <v>00101450</v>
-      </c>
-      <c r="B46" s="8" t="s">
-        <v>167</v>
-      </c>
-      <c r="C46" s="7" t="str">
-        <f>_xlfn.CONCAT("bne 0x",A79)</f>
-        <v>bne 0x001014D4</v>
-      </c>
-      <c r="D46" s="23"/>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A47" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>00101454</v>
-      </c>
-      <c r="B47" s="10" t="s">
+        <v>000DD050</v>
+      </c>
+      <c r="B50" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="C47" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="D47" s="24" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A48" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>00101458</v>
-      </c>
-      <c r="B48" s="10" t="s">
-        <v>169</v>
-      </c>
-      <c r="C48" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="D48" s="24"/>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A49" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>0010145C</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="D49" s="21" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A50" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>00101460</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C50" s="7" t="str">
+        <f>_xlfn.CONCAT("bne 0x",A53)</f>
+        <v>bne 0x000DD05C</v>
+      </c>
+      <c r="D50" s="23"/>
+    </row>
+    <row r="51" spans="1:4">
       <c r="A51" s="2" t="str">
         <f t="shared" si="2"/>
-        <v>00101464</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="C51" s="2" t="str">
-        <f>_xlfn.CONCAT("bhi 0x",A61)</f>
-        <v>bhi 0x0010148C</v>
+        <v>000DD054</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>148</v>
       </c>
       <c r="D51" s="21" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4">
+      <c r="A52" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>000DD058</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C52" s="2" t="str">
+        <f>_xlfn.CONCAT("b 0x",A$104)</f>
+        <v>b 0x001012A4</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4">
+      <c r="A53" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>000DD05C</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="C53" s="2" t="str">
+        <f>C33</f>
+        <v>pop {r4, r5, r6, r7, r8, r10, pc}</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
+      <c r="A55" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B55" s="1"/>
+      <c r="C55" s="1"/>
+      <c r="D55" s="20"/>
+    </row>
+    <row r="56" spans="1:4">
+      <c r="A56" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
+      <c r="A57" s="2" t="str">
+        <f t="shared" ref="A57:A101" si="3">DEC2HEX(HEX2DEC(A56)+4,8)</f>
+        <v>001011F0</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4">
+      <c r="A58" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>001011F4</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4">
+      <c r="A59" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>001011F8</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D59" s="22" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4">
+      <c r="A60" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>001011FC</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D60" s="22"/>
+    </row>
+    <row r="61" spans="1:4">
+      <c r="A61" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>00101200</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D61" s="22"/>
+    </row>
+    <row r="62" spans="1:4">
+      <c r="A62" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>00101204</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D62" s="22"/>
+    </row>
+    <row r="63" spans="1:4">
+      <c r="A63" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>00101208</v>
+      </c>
+      <c r="B63" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C63" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="D63" s="23" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4">
+      <c r="A64" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>0010120C</v>
+      </c>
+      <c r="B64" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C64" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="D64" s="23"/>
+    </row>
+    <row r="65" spans="1:4">
+      <c r="A65" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>00101210</v>
+      </c>
+      <c r="B65" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C65" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D65" s="23"/>
+    </row>
+    <row r="66" spans="1:4">
+      <c r="A66" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>00101214</v>
+      </c>
+      <c r="B66" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="C66" s="7" t="str">
+        <f>_xlfn.CONCAT("bne 0x",A101)</f>
+        <v>bne 0x001012A0</v>
+      </c>
+      <c r="D66" s="23"/>
+    </row>
+    <row r="67" spans="1:4">
+      <c r="A67" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>00101218</v>
+      </c>
+      <c r="B67" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="C67" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="D67" s="24" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4">
+      <c r="A68" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>0010121C</v>
+      </c>
+      <c r="B68" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="C68" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="D68" s="24"/>
+    </row>
+    <row r="69" spans="1:4">
+      <c r="A69" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>00101220</v>
+      </c>
+      <c r="B69" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="C69" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="D69" s="24"/>
+    </row>
+    <row r="70" spans="1:4">
+      <c r="A70" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>00101224</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D70" s="21" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4">
+      <c r="A71" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>00101228</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4">
+      <c r="A72" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>0010122C</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="C72" s="2" t="str">
+        <f>_xlfn.CONCAT("bhi 0x",A83)</f>
+        <v>bhi 0x00101258</v>
+      </c>
+      <c r="D72" s="21" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4">
+      <c r="A73" s="31" t="str">
+        <f t="shared" si="3"/>
+        <v>00101230</v>
+      </c>
+      <c r="B73" s="31" t="s">
+        <v>158</v>
+      </c>
+      <c r="C73" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="D73" s="32" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A52" s="31" t="str">
-        <f t="shared" si="2"/>
-        <v>00101468</v>
-      </c>
-      <c r="B52" s="31" t="s">
-        <v>173</v>
-      </c>
-      <c r="C52" s="31" t="s">
+    <row r="74" spans="1:4">
+      <c r="A74" s="31" t="str">
+        <f t="shared" si="3"/>
+        <v>00101234</v>
+      </c>
+      <c r="B74" s="31" t="s">
+        <v>213</v>
+      </c>
+      <c r="C74" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="D74" s="32"/>
+    </row>
+    <row r="75" spans="1:4">
+      <c r="A75" s="31" t="str">
+        <f t="shared" si="3"/>
+        <v>00101238</v>
+      </c>
+      <c r="B75" s="41" t="s">
+        <v>159</v>
+      </c>
+      <c r="C75" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="D75" s="32"/>
+    </row>
+    <row r="76" spans="1:4">
+      <c r="A76" s="31" t="str">
+        <f t="shared" si="3"/>
+        <v>0010123C</v>
+      </c>
+      <c r="B76" s="31" t="s">
+        <v>214</v>
+      </c>
+      <c r="C76" s="31" t="str">
+        <f>_xlfn.CONCAT("bne 0x",A$101)</f>
+        <v>bne 0x001012A0</v>
+      </c>
+      <c r="D76" s="32"/>
+    </row>
+    <row r="77" spans="1:4">
+      <c r="A77" s="11" t="str">
+        <f t="shared" si="3"/>
+        <v>00101240</v>
+      </c>
+      <c r="B77" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="C77" s="11" t="s">
+        <v>205</v>
+      </c>
+      <c r="D77" s="11"/>
+    </row>
+    <row r="78" spans="1:4">
+      <c r="A78" s="11" t="str">
+        <f t="shared" si="3"/>
+        <v>00101244</v>
+      </c>
+      <c r="B78" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="C78" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="D78" s="11" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4">
+      <c r="A79" s="11" t="str">
+        <f t="shared" si="3"/>
+        <v>00101248</v>
+      </c>
+      <c r="B79" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="C79" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="D79" s="11"/>
+    </row>
+    <row r="80" spans="1:4">
+      <c r="A80" s="11" t="str">
+        <f t="shared" si="3"/>
+        <v>0010124C</v>
+      </c>
+      <c r="B80" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="C80" s="11" t="str">
+        <f>_xlfn.CONCAT("blo 0x",A$101)</f>
+        <v>blo 0x001012A0</v>
+      </c>
+      <c r="D80" s="11" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4">
+      <c r="A81" s="11" t="str">
+        <f t="shared" si="3"/>
+        <v>00101250</v>
+      </c>
+      <c r="B81" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="C81" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="D81" s="11" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4">
+      <c r="A82" s="11" t="str">
+        <f t="shared" si="3"/>
+        <v>00101254</v>
+      </c>
+      <c r="B82" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="C82" s="11" t="str">
+        <f>_xlfn.CONCAT("b 0x",A$104)</f>
+        <v>b 0x001012A4</v>
+      </c>
+      <c r="D82" s="11" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4">
+      <c r="A83" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>00101258</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="C83" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="D52" s="32" t="s">
+      <c r="D83" s="30" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4">
+      <c r="A84" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>0010125C</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="D84" s="30" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4">
+      <c r="A85" s="34" t="str">
+        <f t="shared" si="3"/>
+        <v>00101260</v>
+      </c>
+      <c r="B85" s="34" t="s">
+        <v>158</v>
+      </c>
+      <c r="C85" s="34" t="s">
+        <v>121</v>
+      </c>
+      <c r="D85" s="35" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4">
+      <c r="A86" s="34" t="str">
+        <f t="shared" si="3"/>
+        <v>00101264</v>
+      </c>
+      <c r="B86" s="34" t="s">
+        <v>217</v>
+      </c>
+      <c r="C86" s="34" t="s">
+        <v>122</v>
+      </c>
+      <c r="D86" s="35"/>
+    </row>
+    <row r="87" spans="1:4">
+      <c r="A87" s="34" t="str">
+        <f t="shared" si="3"/>
+        <v>00101268</v>
+      </c>
+      <c r="B87" s="42" t="s">
+        <v>159</v>
+      </c>
+      <c r="C87" s="34" t="s">
+        <v>123</v>
+      </c>
+      <c r="D87" s="35"/>
+    </row>
+    <row r="88" spans="1:4">
+      <c r="A88" s="34" t="str">
+        <f t="shared" si="3"/>
+        <v>0010126C</v>
+      </c>
+      <c r="B88" s="34" t="s">
+        <v>161</v>
+      </c>
+      <c r="C88" s="34" t="str">
+        <f>_xlfn.CONCAT("beq 0x",A$93)</f>
+        <v>beq 0x00101280</v>
+      </c>
+      <c r="D88" s="35"/>
+    </row>
+    <row r="89" spans="1:4">
+      <c r="A89" s="36" t="str">
+        <f t="shared" si="3"/>
+        <v>00101270</v>
+      </c>
+      <c r="B89" s="36" t="s">
+        <v>162</v>
+      </c>
+      <c r="C89" s="36" t="s">
+        <v>136</v>
+      </c>
+      <c r="D89" s="37" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4">
+      <c r="A90" s="36" t="str">
+        <f t="shared" si="3"/>
+        <v>00101274</v>
+      </c>
+      <c r="B90" s="36" t="s">
+        <v>218</v>
+      </c>
+      <c r="C90" s="36" t="s">
+        <v>122</v>
+      </c>
+      <c r="D90" s="37"/>
+    </row>
+    <row r="91" spans="1:4">
+      <c r="A91" s="36" t="str">
+        <f t="shared" si="3"/>
+        <v>00101278</v>
+      </c>
+      <c r="B91" s="43" t="s">
+        <v>159</v>
+      </c>
+      <c r="C91" s="36" t="s">
+        <v>123</v>
+      </c>
+      <c r="D91" s="37"/>
+    </row>
+    <row r="92" spans="1:4">
+      <c r="A92" s="36" t="str">
+        <f t="shared" si="3"/>
+        <v>0010127C</v>
+      </c>
+      <c r="B92" s="36" t="s">
+        <v>163</v>
+      </c>
+      <c r="C92" s="36" t="str">
+        <f>_xlfn.CONCAT("bne 0x",A$101)</f>
+        <v>bne 0x001012A0</v>
+      </c>
+      <c r="D92" s="38"/>
+    </row>
+    <row r="93" spans="1:4">
+      <c r="A93" s="29" t="str">
+        <f t="shared" si="3"/>
+        <v>00101280</v>
+      </c>
+      <c r="B93" s="44" t="s">
+        <v>164</v>
+      </c>
+      <c r="C93" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="D93" s="33" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A53" s="31" t="str">
-        <f t="shared" si="2"/>
-        <v>0010146C</v>
-      </c>
-      <c r="B53" s="31" t="s">
-        <v>174</v>
-      </c>
-      <c r="C53" s="31" t="s">
-        <v>127</v>
-      </c>
-      <c r="D53" s="32"/>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A54" s="31" t="str">
-        <f t="shared" si="2"/>
-        <v>00101470</v>
-      </c>
-      <c r="B54" s="41" t="s">
-        <v>175</v>
-      </c>
-      <c r="C54" s="31" t="s">
-        <v>128</v>
-      </c>
-      <c r="D54" s="32"/>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A55" s="31" t="str">
-        <f t="shared" si="2"/>
-        <v>00101474</v>
-      </c>
-      <c r="B55" s="31" t="s">
-        <v>176</v>
-      </c>
-      <c r="C55" s="31" t="str">
-        <f>_xlfn.CONCAT("bne 0x",A$79)</f>
-        <v>bne 0x001014D4</v>
-      </c>
-      <c r="D55" s="32"/>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A56" s="11" t="str">
-        <f t="shared" si="2"/>
-        <v>00101478</v>
-      </c>
-      <c r="B56" s="11" t="s">
-        <v>177</v>
-      </c>
-      <c r="C56" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="D56" s="11" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A57" s="11" t="str">
-        <f t="shared" si="2"/>
-        <v>0010147C</v>
-      </c>
-      <c r="B57" s="12" t="s">
-        <v>160</v>
-      </c>
-      <c r="C57" s="11" t="s">
+    <row r="94" spans="1:4">
+      <c r="A94" s="29" t="str">
+        <f t="shared" si="3"/>
+        <v>00101284</v>
+      </c>
+      <c r="B94" s="29" t="s">
+        <v>165</v>
+      </c>
+      <c r="C94" s="29" t="s">
+        <v>131</v>
+      </c>
+      <c r="D94" s="33"/>
+    </row>
+    <row r="95" spans="1:4">
+      <c r="A95" s="29" t="str">
+        <f t="shared" si="3"/>
+        <v>00101288</v>
+      </c>
+      <c r="B95" s="29" t="s">
+        <v>161</v>
+      </c>
+      <c r="C95" s="29" t="str">
+        <f>_xlfn.CONCAT("beq 0x",A$100)</f>
+        <v>beq 0x0010129C</v>
+      </c>
+      <c r="D95" s="29"/>
+    </row>
+    <row r="96" spans="1:4">
+      <c r="A96" s="39" t="str">
+        <f t="shared" si="3"/>
+        <v>0010128C</v>
+      </c>
+      <c r="B96" s="39" t="s">
+        <v>166</v>
+      </c>
+      <c r="C96" s="39" t="s">
+        <v>145</v>
+      </c>
+      <c r="D96" s="40" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4">
+      <c r="A97" s="39" t="str">
+        <f t="shared" si="3"/>
+        <v>00101290</v>
+      </c>
+      <c r="B97" s="45" t="s">
+        <v>167</v>
+      </c>
+      <c r="C97" s="39" t="s">
+        <v>143</v>
+      </c>
+      <c r="D97" s="40" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4">
+      <c r="A98" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>00101294</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C98" s="2" t="str">
+        <f>_xlfn.CONCAT("bne 0x",A$101)</f>
+        <v>bne 0x001012A0</v>
+      </c>
+      <c r="D98" s="30" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4">
+      <c r="A99" s="39" t="str">
+        <f t="shared" si="3"/>
+        <v>00101298</v>
+      </c>
+      <c r="B99" s="39" t="s">
+        <v>169</v>
+      </c>
+      <c r="C99" s="39" t="s">
+        <v>148</v>
+      </c>
+      <c r="D99" s="40" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4">
+      <c r="A100" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>0010129C</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="C100" s="2" t="str">
+        <f>_xlfn.CONCAT("b 0x",A$104)</f>
+        <v>b 0x001012A4</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4">
+      <c r="A101" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>001012A0</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="C101" s="2" t="str">
+        <f>C33</f>
+        <v>pop {r4, r5, r6, r7, r8, r10, pc}</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" ht="47.6">
+      <c r="A103" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D103" s="21" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4">
+      <c r="A104" s="2" t="str">
+        <f>DEC2HEX(HEX2DEC(A101)+4,8)</f>
+        <v>001012A4</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D104" s="21" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4">
+      <c r="A105" s="4" t="str">
+        <f t="shared" ref="A105:A136" si="4">DEC2HEX(HEX2DEC(A104)+4,8)</f>
+        <v>001012A8</v>
+      </c>
+      <c r="B105" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="C105" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="D57" s="11"/>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A58" s="11" t="str">
-        <f t="shared" si="2"/>
-        <v>00101480</v>
-      </c>
-      <c r="B58" s="11" t="s">
+      <c r="D105" s="22" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4">
+      <c r="A106" s="7" t="str">
+        <f t="shared" si="4"/>
+        <v>001012AC</v>
+      </c>
+      <c r="B106" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="C106" s="7" t="str">
+        <f>_xlfn.CONCAT("bne 0x",A111)</f>
+        <v>bne 0x001012C0</v>
+      </c>
+      <c r="D106" s="23" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4">
+      <c r="A107" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v>001012B0</v>
+      </c>
+      <c r="B107" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="C107" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="D107" s="22" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4">
+      <c r="A108" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v>001012B4</v>
+      </c>
+      <c r="B108" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="C108" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="D108" s="22" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4">
+      <c r="A109" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v>001012B8</v>
+      </c>
+      <c r="B109" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="C109" s="4" t="str">
+        <f>_xlfn.CONCAT("bne 0x",A136)</f>
+        <v>bne 0x00101324</v>
+      </c>
+      <c r="D109" s="22"/>
+    </row>
+    <row r="110" spans="1:4">
+      <c r="A110" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v>001012BC</v>
+      </c>
+      <c r="B110" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="C110" s="4" t="str">
+        <f>_xlfn.CONCAT("b 0x",A$114)</f>
+        <v>b 0x001012CC</v>
+      </c>
+      <c r="D110" s="22"/>
+    </row>
+    <row r="111" spans="1:4">
+      <c r="A111" s="7" t="str">
+        <f t="shared" si="4"/>
+        <v>001012C0</v>
+      </c>
+      <c r="B111" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="C111" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="D111" s="23" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4">
+      <c r="A112" s="7" t="str">
+        <f t="shared" si="4"/>
+        <v>001012C4</v>
+      </c>
+      <c r="B112" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="C112" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="D112" s="23" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4">
+      <c r="A113" s="7" t="str">
+        <f t="shared" si="4"/>
+        <v>001012C8</v>
+      </c>
+      <c r="B113" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="C113" s="7" t="str">
+        <f>_xlfn.CONCAT("beq 0x",A136)</f>
+        <v>beq 0x00101324</v>
+      </c>
+      <c r="D113" s="23"/>
+    </row>
+    <row r="114" spans="1:4">
+      <c r="A114" s="9" t="str">
+        <f t="shared" si="4"/>
+        <v>001012CC</v>
+      </c>
+      <c r="B114" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="C114" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="D114" s="24" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4">
+      <c r="A115" s="9" t="str">
+        <f t="shared" si="4"/>
+        <v>001012D0</v>
+      </c>
+      <c r="B115" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C115" s="9" t="str">
+        <f>_xlfn.CONCAT("beq 0x",A$136)</f>
+        <v>beq 0x00101324</v>
+      </c>
+      <c r="D115" s="24" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4">
+      <c r="A116" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>001012D4</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4">
+      <c r="A117" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>001012D8</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4">
+      <c r="A118" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>001012DC</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4">
+      <c r="A119" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>001012E0</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C119" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4">
+      <c r="A120" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>001012E4</v>
+      </c>
+      <c r="B120" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4">
+      <c r="A121" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>001012E8</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D121" s="21" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4">
+      <c r="A122" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>001012EC</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D122" s="21" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4">
+      <c r="A123" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>001012F0</v>
+      </c>
+      <c r="B123" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4">
+      <c r="A124" s="18" t="str">
+        <f t="shared" si="4"/>
+        <v>001012F4</v>
+      </c>
+      <c r="B124" s="19" t="s">
+        <v>154</v>
+      </c>
+      <c r="C124" s="18" t="s">
+        <v>117</v>
+      </c>
+      <c r="D124" s="28" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4">
+      <c r="A125" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>001012F8</v>
+      </c>
+      <c r="B125" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4">
+      <c r="A126" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>001012FC</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4">
+      <c r="A127" s="18" t="str">
+        <f t="shared" si="4"/>
+        <v>00101300</v>
+      </c>
+      <c r="B127" s="18" t="s">
         <v>201</v>
       </c>
-      <c r="C58" s="11" t="str">
-        <f>_xlfn.CONCAT("blo 0x",A$79)</f>
-        <v>blo 0x001014D4</v>
-      </c>
-      <c r="D58" s="11" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A59" s="11" t="str">
-        <f t="shared" si="2"/>
-        <v>00101484</v>
-      </c>
-      <c r="B59" s="12" t="s">
+      <c r="C127" s="18" t="s">
+        <v>198</v>
+      </c>
+      <c r="D127" s="28" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4">
+      <c r="A128" s="18" t="str">
+        <f t="shared" si="4"/>
+        <v>00101304</v>
+      </c>
+      <c r="B128" s="19" t="s">
         <v>202</v>
       </c>
-      <c r="C59" s="11" t="s">
-        <v>200</v>
-      </c>
-      <c r="D59" s="11" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A60" s="11" t="str">
-        <f t="shared" si="2"/>
-        <v>00101488</v>
-      </c>
-      <c r="B60" s="11" t="s">
-        <v>203</v>
-      </c>
-      <c r="C60" s="11" t="str">
-        <f>_xlfn.CONCAT("b 0x",A$82)</f>
-        <v>b 0x001014D8</v>
-      </c>
-      <c r="D60" s="11" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A61" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>0010148C</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="D61" s="30" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A62" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>00101490</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="D62" s="30" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A63" s="34" t="str">
-        <f t="shared" si="2"/>
-        <v>00101494</v>
-      </c>
-      <c r="B63" s="34" t="s">
-        <v>173</v>
-      </c>
-      <c r="C63" s="34" t="s">
-        <v>126</v>
-      </c>
-      <c r="D63" s="35" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A64" s="34" t="str">
-        <f t="shared" si="2"/>
-        <v>00101498</v>
-      </c>
-      <c r="B64" s="34" t="s">
-        <v>180</v>
-      </c>
-      <c r="C64" s="34" t="s">
-        <v>127</v>
-      </c>
-      <c r="D64" s="35"/>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A65" s="34" t="str">
-        <f t="shared" si="2"/>
-        <v>0010149C</v>
-      </c>
-      <c r="B65" s="42" t="s">
-        <v>175</v>
-      </c>
-      <c r="C65" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="D65" s="35"/>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A66" s="34" t="str">
-        <f t="shared" si="2"/>
-        <v>001014A0</v>
-      </c>
-      <c r="B66" s="34" t="s">
-        <v>181</v>
-      </c>
-      <c r="C66" s="34" t="str">
-        <f>_xlfn.CONCAT("beq 0x",A$71)</f>
-        <v>beq 0x001014B4</v>
-      </c>
-      <c r="D66" s="35"/>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A67" s="36" t="str">
-        <f t="shared" si="2"/>
-        <v>001014A4</v>
-      </c>
-      <c r="B67" s="36" t="s">
-        <v>182</v>
-      </c>
-      <c r="C67" s="36" t="s">
-        <v>142</v>
-      </c>
-      <c r="D67" s="37" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A68" s="36" t="str">
-        <f t="shared" si="2"/>
-        <v>001014A8</v>
-      </c>
-      <c r="B68" s="36" t="s">
-        <v>183</v>
-      </c>
-      <c r="C68" s="36" t="s">
-        <v>127</v>
-      </c>
-      <c r="D68" s="37"/>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A69" s="36" t="str">
-        <f t="shared" si="2"/>
-        <v>001014AC</v>
-      </c>
-      <c r="B69" s="43" t="s">
-        <v>175</v>
-      </c>
-      <c r="C69" s="36" t="s">
-        <v>128</v>
-      </c>
-      <c r="D69" s="37"/>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A70" s="36" t="str">
-        <f t="shared" si="2"/>
-        <v>001014B0</v>
-      </c>
-      <c r="B70" s="36" t="s">
-        <v>184</v>
-      </c>
-      <c r="C70" s="36" t="str">
-        <f>_xlfn.CONCAT("bne 0x",A$79)</f>
-        <v>bne 0x001014D4</v>
-      </c>
-      <c r="D70" s="38"/>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A71" s="29" t="str">
-        <f t="shared" si="2"/>
-        <v>001014B4</v>
-      </c>
-      <c r="B71" s="44" t="s">
-        <v>185</v>
-      </c>
-      <c r="C71" s="29" t="s">
-        <v>147</v>
-      </c>
-      <c r="D71" s="33" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A72" s="29" t="str">
-        <f t="shared" si="2"/>
-        <v>001014B8</v>
-      </c>
-      <c r="B72" s="29" t="s">
-        <v>186</v>
-      </c>
-      <c r="C72" s="29" t="s">
-        <v>137</v>
-      </c>
-      <c r="D72" s="33"/>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A73" s="29" t="str">
-        <f t="shared" si="2"/>
-        <v>001014BC</v>
-      </c>
-      <c r="B73" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="C73" s="29" t="str">
-        <f>_xlfn.CONCAT("beq 0x",A$78)</f>
-        <v>beq 0x001014D0</v>
-      </c>
-      <c r="D73" s="29"/>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A74" s="39" t="str">
-        <f t="shared" si="2"/>
-        <v>001014C0</v>
-      </c>
-      <c r="B74" s="39" t="s">
-        <v>187</v>
-      </c>
-      <c r="C74" s="39" t="s">
-        <v>151</v>
-      </c>
-      <c r="D74" s="40" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A75" s="39" t="str">
-        <f t="shared" si="2"/>
-        <v>001014C4</v>
-      </c>
-      <c r="B75" s="45" t="s">
-        <v>188</v>
-      </c>
-      <c r="C75" s="39" t="s">
-        <v>149</v>
-      </c>
-      <c r="D75" s="40" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A76" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>001014C8</v>
-      </c>
-      <c r="B76" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="C76" s="2" t="str">
-        <f>_xlfn.CONCAT("bne 0x",A$79)</f>
-        <v>bne 0x001014D4</v>
-      </c>
-      <c r="D76" s="30" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A77" s="39" t="str">
-        <f t="shared" si="2"/>
-        <v>001014CC</v>
-      </c>
-      <c r="B77" s="39" t="s">
-        <v>190</v>
-      </c>
-      <c r="C77" s="39" t="s">
-        <v>154</v>
-      </c>
-      <c r="D77" s="40" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A78" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>001014D0</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="C78" s="2" t="str">
-        <f>_xlfn.CONCAT("b 0x",A$82)</f>
-        <v>b 0x001014D8</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A79" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>001014D4</v>
-      </c>
-      <c r="B79" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C79" s="2" t="str">
-        <f>C33</f>
-        <v>pop {r4, r5, r6, r7, r8, pc}</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" ht="47.6" x14ac:dyDescent="0.45">
-      <c r="A81" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="D81" s="21" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A82" s="2" t="str">
-        <f>DEC2HEX(HEX2DEC(A79)+4,8)</f>
-        <v>001014D8</v>
-      </c>
-      <c r="B82" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="D82" s="21" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A83" s="4" t="str">
-        <f t="shared" ref="A83:A87" si="3">DEC2HEX(HEX2DEC(A82)+4,8)</f>
-        <v>001014DC</v>
-      </c>
-      <c r="B83" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="C83" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="D83" s="22" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A84" s="7" t="str">
-        <f t="shared" si="3"/>
-        <v>001014E0</v>
-      </c>
-      <c r="B84" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="C84" s="7" t="str">
-        <f>_xlfn.CONCAT("bne 0x",A88)</f>
-        <v>bne 0x001014F0</v>
-      </c>
-      <c r="D84" s="23" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A85" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>001014E4</v>
-      </c>
-      <c r="B85" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="C85" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="D85" s="22" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A86" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>001014E8</v>
-      </c>
-      <c r="B86" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="C86" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="D86" s="22" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A87" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>001014EC</v>
-      </c>
-      <c r="B87" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="C87" s="4" t="str">
-        <f>_xlfn.CONCAT("b 0x",A$90)</f>
-        <v>b 0x001014F8</v>
-      </c>
-      <c r="D87" s="22"/>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A88" s="7" t="str">
-        <f t="shared" ref="A88:A95" si="4">DEC2HEX(HEX2DEC(A87)+4,8)</f>
-        <v>001014F0</v>
-      </c>
-      <c r="B88" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="C88" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="D88" s="23" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A89" s="7" t="str">
+      <c r="C128" s="18" t="s">
+        <v>197</v>
+      </c>
+      <c r="D128" s="28" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3">
+      <c r="A129" s="2" t="str">
         <f t="shared" si="4"/>
-        <v>001014F4</v>
-      </c>
-      <c r="B89" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="C89" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="D89" s="23" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A90" s="9" t="str">
+        <v>00101308</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C129" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3">
+      <c r="A130" s="2" t="str">
         <f t="shared" si="4"/>
-        <v>001014F8</v>
-      </c>
-      <c r="B90" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="C90" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="D90" s="24" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A91" s="9" t="str">
+        <v>0010130C</v>
+      </c>
+      <c r="B130" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3">
+      <c r="A131" s="2" t="str">
         <f t="shared" si="4"/>
-        <v>001014FC</v>
-      </c>
-      <c r="B91" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="C91" s="9" t="str">
-        <f>_xlfn.CONCAT("beq 0x",A$112)</f>
-        <v>beq 0x00101550</v>
-      </c>
-      <c r="D91" s="24" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A92" s="2" t="str">
+        <v>00101310</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="C131" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3">
+      <c r="A132" s="2" t="str">
         <f t="shared" si="4"/>
-        <v>00101500</v>
-      </c>
-      <c r="B92" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C92" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A93" s="2" t="str">
+        <v>00101314</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C132" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3">
+      <c r="A133" s="2" t="str">
         <f t="shared" si="4"/>
-        <v>00101504</v>
-      </c>
-      <c r="B93" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C93" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A94" s="2" t="str">
+        <v>00101318</v>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3">
+      <c r="A134" s="2" t="str">
         <f t="shared" si="4"/>
-        <v>00101508</v>
-      </c>
-      <c r="B94" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C94" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A95" s="2" t="str">
+        <v>0010131C</v>
+      </c>
+      <c r="B134" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="C134" s="2" t="str">
+        <f>SUBSTITUTE(C11,"push","pop")</f>
+        <v>pop {r4, r5, r6, r7, r8, r10, lr}</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3">
+      <c r="A135" s="2" t="str">
         <f t="shared" si="4"/>
-        <v>0010150C</v>
-      </c>
-      <c r="B95" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="C95" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A96" s="2" t="str">
-        <f>DEC2HEX(HEX2DEC(A95)+4,8)</f>
-        <v>00101510</v>
-      </c>
-      <c r="B96" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C96" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A97" s="2" t="str">
-        <f t="shared" ref="A97:A112" si="5">DEC2HEX(HEX2DEC(A96)+4,8)</f>
-        <v>00101514</v>
-      </c>
-      <c r="B97" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C97" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A98" s="2" t="str">
-        <f t="shared" si="5"/>
-        <v>00101518</v>
-      </c>
-      <c r="B98" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C98" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A99" s="2" t="str">
-        <f t="shared" si="5"/>
-        <v>0010151C</v>
-      </c>
-      <c r="B99" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C99" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A100" s="18" t="str">
-        <f t="shared" si="5"/>
-        <v>00101520</v>
-      </c>
-      <c r="B100" s="19" t="s">
-        <v>162</v>
-      </c>
-      <c r="C100" s="18" t="s">
-        <v>120</v>
-      </c>
-      <c r="D100" s="28" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A101" s="2" t="str">
-        <f t="shared" si="5"/>
-        <v>00101524</v>
-      </c>
-      <c r="B101" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C101" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A102" s="2" t="str">
-        <f t="shared" si="5"/>
-        <v>00101528</v>
-      </c>
-      <c r="B102" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C102" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A103" s="18" t="str">
-        <f t="shared" si="5"/>
-        <v>0010152C</v>
-      </c>
-      <c r="B103" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="C103" s="18" t="s">
-        <v>79</v>
-      </c>
-      <c r="D103" s="28" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A104" s="18" t="str">
-        <f t="shared" si="5"/>
-        <v>00101530</v>
-      </c>
-      <c r="B104" s="19" t="s">
-        <v>56</v>
-      </c>
-      <c r="C104" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="D104" s="28" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A105" s="2" t="str">
-        <f t="shared" si="5"/>
-        <v>00101534</v>
-      </c>
-      <c r="B105" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C105" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A106" s="2" t="str">
-        <f t="shared" si="5"/>
-        <v>00101538</v>
-      </c>
-      <c r="B106" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C106" s="2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A107" s="2" t="str">
-        <f t="shared" si="5"/>
-        <v>0010153C</v>
-      </c>
-      <c r="B107" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="C107" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A108" s="2" t="str">
-        <f t="shared" si="5"/>
-        <v>00101540</v>
-      </c>
-      <c r="B108" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C108" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A109" s="2" t="str">
-        <f t="shared" si="5"/>
-        <v>00101544</v>
-      </c>
-      <c r="B109" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C109" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A110" s="2" t="str">
-        <f t="shared" si="5"/>
-        <v>00101548</v>
-      </c>
-      <c r="B110" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C110" s="2" t="str">
-        <f>SUBSTITUTE(C11,"push","pop")</f>
-        <v>pop {r4, r5, r6, r7, r8, lr}</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A111" s="2" t="str">
-        <f t="shared" si="5"/>
-        <v>0010154C</v>
-      </c>
-      <c r="B111" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="C111" s="2" t="s">
+        <v>00101320</v>
+      </c>
+      <c r="B135" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="C135" s="2" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A112" s="2" t="str">
-        <f t="shared" si="5"/>
-        <v>00101550</v>
-      </c>
-      <c r="B112" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C112" s="2" t="str">
-        <f>SUBSTITUTE(C110,"lr","pc")</f>
-        <v>pop {r4, r5, r6, r7, r8, pc}</v>
+    <row r="136" spans="1:3">
+      <c r="A136" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>00101324</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="C136" s="2" t="str">
+        <f>SUBSTITUTE(C134,"lr","pc")</f>
+        <v>pop {r4, r5, r6, r7, r8, r10, pc}</v>
       </c>
     </row>
   </sheetData>
@@ -2698,18 +3098,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC3FF682-529F-445E-A539-EDFF7BE80E58}">
   <dimension ref="A1:F55"/>
-  <sheetFormatPr defaultRowHeight="15.9" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="9.2109375" defaultRowHeight="15.9"/>
   <cols>
-    <col min="1" max="1" width="10.84375" style="2" customWidth="1"/>
-    <col min="2" max="2" width="10.07421875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.23046875" style="2" customWidth="1"/>
-    <col min="5" max="8" width="9.23046875" style="2"/>
-    <col min="9" max="11" width="2.3046875" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.23046875" style="2"/>
+    <col min="1" max="1" width="10.85546875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="10.0703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.78515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.2109375" style="2" customWidth="1"/>
+    <col min="5" max="8" width="9.2109375" style="2"/>
+    <col min="9" max="11" width="2.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="9.2109375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -2723,7 +3123,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
         <v>92</v>
       </c>
@@ -2731,7 +3131,7 @@
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:6">
       <c r="A3" s="2" t="s">
         <v>99</v>
       </c>
@@ -2744,7 +3144,7 @@
       </c>
       <c r="D3" s="1"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:6">
       <c r="A4" s="2" t="str">
         <f t="shared" ref="A4:A7" si="0">DEC2HEX(HEX2DEC(A3)+4,8)</f>
         <v>000D9EE8</v>
@@ -2757,7 +3157,7 @@
       </c>
       <c r="D4" s="1"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:6">
       <c r="A5" s="2" t="str">
         <f t="shared" si="0"/>
         <v>000D9EEC</v>
@@ -2770,7 +3170,7 @@
       </c>
       <c r="D5" s="1"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:6">
       <c r="A6" s="2" t="str">
         <f t="shared" si="0"/>
         <v>000D9EF0</v>
@@ -2783,7 +3183,7 @@
       </c>
       <c r="D6" s="1"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:6">
       <c r="A7" s="2" t="str">
         <f t="shared" si="0"/>
         <v>000D9EF4</v>
@@ -2796,16 +3196,16 @@
       </c>
       <c r="D7" s="1"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:6">
       <c r="D8" s="1"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:6">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:6">
       <c r="A10" s="1" t="s">
         <v>0</v>
       </c>
@@ -2813,7 +3213,7 @@
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:6">
       <c r="A11" s="3" t="s">
         <v>14</v>
       </c>
@@ -2824,7 +3224,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:6">
       <c r="A12" s="2" t="str">
         <f t="shared" ref="A12:A55" si="1">DEC2HEX(HEX2DEC(A11)+4,8)</f>
         <v>000D6F9C</v>
@@ -2836,7 +3236,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:6">
       <c r="A13" s="2" t="str">
         <f t="shared" si="1"/>
         <v>000D6FA0</v>
@@ -2848,7 +3248,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:6">
       <c r="A14" s="4" t="str">
         <f t="shared" si="1"/>
         <v>000D6FA4</v>
@@ -2863,7 +3263,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:6">
       <c r="A15" s="4" t="str">
         <f t="shared" si="1"/>
         <v>000D6FA8</v>
@@ -2876,7 +3276,7 @@
       </c>
       <c r="D15" s="4"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:6">
       <c r="A16" s="4" t="str">
         <f t="shared" si="1"/>
         <v>000D6FAC</v>
@@ -2891,7 +3291,7 @@
       <c r="E16" s="6"/>
       <c r="F16" s="6"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:6">
       <c r="A17" s="4" t="str">
         <f t="shared" si="1"/>
         <v>000D6FB0</v>
@@ -2906,7 +3306,7 @@
       <c r="E17" s="6"/>
       <c r="F17" s="6"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:6">
       <c r="A18" s="7" t="str">
         <f t="shared" si="1"/>
         <v>000D6FB4</v>
@@ -2923,7 +3323,7 @@
       <c r="E18" s="6"/>
       <c r="F18" s="6"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:6">
       <c r="A19" s="7" t="str">
         <f t="shared" si="1"/>
         <v>000D6FB8</v>
@@ -2938,7 +3338,7 @@
       <c r="E19" s="6"/>
       <c r="F19" s="6"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:6">
       <c r="A20" s="7" t="str">
         <f t="shared" si="1"/>
         <v>000D6FBC</v>
@@ -2952,7 +3352,7 @@
       <c r="D20" s="7"/>
       <c r="F20" s="6"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:6">
       <c r="A21" s="7" t="str">
         <f t="shared" si="1"/>
         <v>000D6FC0</v>
@@ -2968,7 +3368,7 @@
       <c r="E21" s="6"/>
       <c r="F21" s="6"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:6">
       <c r="A22" s="9" t="str">
         <f t="shared" si="1"/>
         <v>000D6FC4</v>
@@ -2983,7 +3383,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:6">
       <c r="A23" s="9" t="str">
         <f t="shared" si="1"/>
         <v>000D6FC8</v>
@@ -2996,7 +3396,7 @@
       </c>
       <c r="D23" s="9"/>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:6">
       <c r="A24" s="9" t="str">
         <f t="shared" si="1"/>
         <v>000D6FCC</v>
@@ -3009,7 +3409,7 @@
       </c>
       <c r="D24" s="9"/>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:6">
       <c r="A25" s="9" t="str">
         <f t="shared" si="1"/>
         <v>000D6FD0</v>
@@ -3022,7 +3422,7 @@
       </c>
       <c r="D25" s="9"/>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:6">
       <c r="A26" s="11" t="str">
         <f t="shared" si="1"/>
         <v>000D6FD4</v>
@@ -3037,7 +3437,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:6">
       <c r="A27" s="11" t="str">
         <f t="shared" si="1"/>
         <v>000D6FD8</v>
@@ -3050,7 +3450,7 @@
       </c>
       <c r="D27" s="13"/>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:6">
       <c r="A28" s="11" t="str">
         <f t="shared" si="1"/>
         <v>000D6FDC</v>
@@ -3063,7 +3463,7 @@
       </c>
       <c r="D28" s="11"/>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:6">
       <c r="A29" s="14" t="str">
         <f t="shared" si="1"/>
         <v>000D6FE0</v>
@@ -3078,7 +3478,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:6">
       <c r="A30" s="16" t="str">
         <f t="shared" si="1"/>
         <v>000D6FE4</v>
@@ -3093,7 +3493,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:6">
       <c r="A31" s="14" t="str">
         <f t="shared" si="1"/>
         <v>000D6FE8</v>
@@ -3108,7 +3508,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:6">
       <c r="A32" s="14" t="str">
         <f t="shared" si="1"/>
         <v>000D6FEC</v>
@@ -3121,7 +3521,7 @@
       </c>
       <c r="D32" s="14"/>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:4">
       <c r="A33" s="16" t="str">
         <f t="shared" si="1"/>
         <v>000D6FF0</v>
@@ -3134,7 +3534,7 @@
       </c>
       <c r="D33" s="16"/>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:4">
       <c r="A34" s="16" t="str">
         <f t="shared" si="1"/>
         <v>000D6FF4</v>
@@ -3148,7 +3548,7 @@
       </c>
       <c r="D34" s="16"/>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:4">
       <c r="A35" s="2" t="str">
         <f t="shared" si="1"/>
         <v>000D6FF8</v>
@@ -3160,7 +3560,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:4">
       <c r="A36" s="2" t="str">
         <f t="shared" si="1"/>
         <v>000D6FFC</v>
@@ -3172,7 +3572,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:4">
       <c r="A37" s="2" t="str">
         <f t="shared" si="1"/>
         <v>000D7000</v>
@@ -3184,7 +3584,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:4">
       <c r="A38" s="2" t="str">
         <f t="shared" si="1"/>
         <v>000D7004</v>
@@ -3196,7 +3596,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:4">
       <c r="A39" s="2" t="str">
         <f t="shared" si="1"/>
         <v>000D7008</v>
@@ -3208,7 +3608,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:4">
       <c r="A40" s="2" t="str">
         <f t="shared" si="1"/>
         <v>000D700C</v>
@@ -3220,7 +3620,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:4">
       <c r="A41" s="2" t="str">
         <f t="shared" si="1"/>
         <v>000D7010</v>
@@ -3232,7 +3632,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:4">
       <c r="A42" s="2" t="str">
         <f t="shared" si="1"/>
         <v>000D7014</v>
@@ -3244,7 +3644,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:4">
       <c r="A43" s="18" t="str">
         <f t="shared" si="1"/>
         <v>000D7018</v>
@@ -3259,7 +3659,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:4">
       <c r="A44" s="2" t="str">
         <f t="shared" si="1"/>
         <v>000D701C</v>
@@ -3271,7 +3671,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:4">
       <c r="A45" s="2" t="str">
         <f t="shared" si="1"/>
         <v>000D7020</v>
@@ -3283,7 +3683,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:4">
       <c r="A46" s="18" t="str">
         <f t="shared" si="1"/>
         <v>000D7024</v>
@@ -3296,7 +3696,7 @@
       </c>
       <c r="D46" s="18"/>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:4">
       <c r="A47" s="18" t="str">
         <f t="shared" si="1"/>
         <v>000D7028</v>
@@ -3309,7 +3709,7 @@
       </c>
       <c r="D47" s="18"/>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:4">
       <c r="A48" s="2" t="str">
         <f t="shared" si="1"/>
         <v>000D702C</v>
@@ -3321,7 +3721,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:3">
       <c r="A49" s="2" t="str">
         <f t="shared" si="1"/>
         <v>000D7030</v>
@@ -3333,7 +3733,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:3">
       <c r="A50" s="2" t="str">
         <f t="shared" si="1"/>
         <v>000D7034</v>
@@ -3345,7 +3745,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:3">
       <c r="A51" s="2" t="str">
         <f t="shared" si="1"/>
         <v>000D7038</v>
@@ -3357,7 +3757,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:3">
       <c r="A52" s="2" t="str">
         <f t="shared" si="1"/>
         <v>000D703C</v>
@@ -3369,7 +3769,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:3">
       <c r="A53" s="2" t="str">
         <f t="shared" si="1"/>
         <v>000D7040</v>
@@ -3382,7 +3782,7 @@
         <v>pop {r4, r5, r6, r7, r8, lr}</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:3">
       <c r="A54" s="2" t="str">
         <f t="shared" si="1"/>
         <v>000D7044</v>
@@ -3394,7 +3794,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:3">
       <c r="A55" s="2" t="str">
         <f t="shared" si="1"/>
         <v>000D7048</v>
